--- a/Fittech/過站/20260715.xlsx
+++ b/Fittech/過站/20260715.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary_kuo\Desktop\過站\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\ImpDocuments\Fittech\過站\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AF74E8-4623-463A-9E2A-FA5F13B78308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD743709-3D20-4BDF-8F26-3A91D37D6F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{8FE51230-3E2D-471B-9C31-3D38E118EC81}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8FE51230-3E2D-471B-9C31-3D38E118EC81}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>WaferID</t>
   </si>
@@ -132,15 +135,6 @@
     <t>LBT20</t>
   </si>
   <si>
-    <t>RT387232</t>
-  </si>
-  <si>
-    <t>LBT03</t>
-  </si>
-  <si>
-    <t>B2995495 F998有1顆</t>
-  </si>
-  <si>
     <t>WL390364</t>
   </si>
   <si>
@@ -171,10 +165,6 @@
   </si>
   <si>
     <t>LBT22 B3012101良率:15.44% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>扣帳後可過站</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -655,15 +645,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485961E4-91FE-4B9A-91AE-70839D9BB191}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -707,7 +696,7 @@
       <c r="E2" s="10"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -766,7 +755,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -784,10 +773,10 @@
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -805,10 +794,10 @@
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -826,10 +815,10 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -847,10 +836,10 @@
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -867,11 +856,11 @@
         <v>46217.182256944441</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -879,66 +868,46 @@
         <v>32</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D14" s="12">
-        <v>46218.062199074076</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>34</v>
+        <v>46218.231030092589</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D15" s="12">
-        <v>46218.231030092589</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>43</v>
+        <v>46218.311851851853</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="12">
-        <v>46218.311851851853</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Fittech/過站/20260715.xlsx
+++ b/Fittech/過站/20260715.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\ImpDocuments\Fittech\過站\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD743709-3D20-4BDF-8F26-3A91D37D6F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957153D0-872E-42E4-8175-5E5A661071C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8FE51230-3E2D-471B-9C31-3D38E118EC81}"/>
   </bookViews>
@@ -129,66 +129,68 @@
     <t>WL391106</t>
   </si>
   <si>
+    <t>LBT20</t>
+  </si>
+  <si>
+    <t>RL391691</t>
+  </si>
+  <si>
+    <t>整個Wafer有重複ID請工程確認！</t>
+  </si>
+  <si>
+    <t>LBT22 B3012219良率:38.31% &lt; 40%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBT10 B2995441良率:35.24% &lt; 40%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBT21 B3008103良率:33.49% &lt; 40%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBT21 B3012189良率:38.94% &lt; 40%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBT20 B3018209良率:35.95% &lt; 40%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBT22 B3012101良率:15.44% &lt; 40%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>實體重複</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>良率超低待確認</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>準備重工</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已寄信(7/15)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>品保發待odin回信(7/13)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>WL394060</t>
-  </si>
-  <si>
-    <t>LBT20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>待寄信</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>WL390364</t>
-  </si>
-  <si>
-    <t>RL391691</t>
-  </si>
-  <si>
-    <t>整個Wafer有重複ID請工程確認！</t>
-  </si>
-  <si>
-    <t>LBT22 B3012219良率:38.31% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBT10 B2995441良率:35.24% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBT21 B3008103良率:33.49% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBT21 B3012189良率:38.94% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBT20 B3018209良率:35.95% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBT22 B3012101良率:15.44% &lt; 40%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>實體重複</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>良率超低待確認</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>準備重工</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>確認中</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已寄信(7/15)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>品保發待odin回信(7/13)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -696,7 +698,7 @@
       <c r="E2" s="10"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -755,7 +757,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -773,10 +775,10 @@
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -794,10 +796,10 @@
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -815,10 +817,10 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -836,36 +838,36 @@
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="11" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="12">
         <v>46217.182256944441</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="11" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>23</v>
@@ -877,16 +879,16 @@
         <v>46218.231030092589</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>25</v>
@@ -898,11 +900,11 @@
         <v>46218.311851851853</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
